--- a/ml_server/data/EnPhiSim_dataset.xlsx
+++ b/ml_server/data/EnPhiSim_dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DIVYATEJ\OneDrive\EnPhiSim_clean\ml_server\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d8bb43d649376014/EnPhiSim_clean/ml_server/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57DEAB4-2794-4FE9-BD34-575627185745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{D57DEAB4-2794-4FE9-BD34-575627185745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90F45010-933A-4050-A6FB-C43EDC269E3B}"/>
   <bookViews>
-    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{652C4A2D-35AE-4F6D-9BD4-8B9990ADAB74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{652C4A2D-35AE-4F6D-9BD4-8B9990ADAB74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
